--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261016.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261016.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>312,623,360</t>
+          <t>2,229,422</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,229,422</t>
+          <t>1,906,111</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,906,111</t>
+          <t>312,623,360</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>30,603,129</t>
+          <t>7,351,530</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>7,351,530</t>
+          <t>30,603,129</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>27,128,300</t>
+          <t>10,938,955</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>10,938,955</t>
+          <t>27,128,300</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
